--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/property/tax_sale/index.php?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/property-tax/tax-sale-excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17796,7 +17796,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,142 +429,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Parcel_ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Verify_Note</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Source_URL</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Record_Type</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Retrieved_At</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -681,12 +693,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -759,7 +771,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -813,12 +825,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -891,7 +903,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +957,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1035,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1077,12 +1089,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1167,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1209,12 +1221,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1299,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1431,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1473,12 +1485,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1563,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1605,12 +1617,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1695,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1737,12 +1749,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1827,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1869,12 +1881,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1959,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2001,12 +2013,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2091,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2133,12 +2145,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2223,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2265,12 +2277,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2355,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2397,12 +2409,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2487,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2529,12 +2541,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2619,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2661,12 +2673,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2751,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2793,12 +2805,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2883,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2925,12 +2937,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3015,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3057,12 +3069,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3147,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3189,12 +3201,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3279,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3321,12 +3333,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3411,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3453,12 +3465,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3543,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3585,12 +3597,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3675,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3717,12 +3729,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3807,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3849,12 +3861,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3939,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3981,12 +3993,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4071,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4113,12 +4125,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4203,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4245,12 +4257,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4335,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4377,12 +4389,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4467,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4509,12 +4521,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4599,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4641,12 +4653,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4731,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4773,12 +4785,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4863,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4905,12 +4917,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4995,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5037,12 +5049,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5127,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5169,12 +5181,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5259,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5301,12 +5313,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5391,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5433,12 +5445,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5523,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5565,12 +5577,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5655,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5697,12 +5709,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5787,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5829,12 +5841,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5919,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5961,12 +5973,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6083,12 +6095,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6173,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6215,12 +6227,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6349,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6427,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6469,12 +6481,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6559,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6601,12 +6613,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6691,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6733,12 +6745,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6823,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6865,12 +6877,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6955,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6997,12 +7009,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7129,12 +7141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7219,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7261,12 +7273,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7351,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7393,12 +7405,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7483,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7525,12 +7537,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7615,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7657,12 +7669,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7747,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7789,12 +7801,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7879,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7921,12 +7933,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8011,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8053,12 +8065,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8143,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8185,12 +8197,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8275,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8317,12 +8329,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8407,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8449,12 +8461,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8539,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8581,12 +8593,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8671,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8713,12 +8725,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8803,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8845,12 +8857,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8935,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8977,12 +8989,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9067,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9109,12 +9121,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9199,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9241,12 +9253,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9331,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9373,12 +9385,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9463,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9505,12 +9517,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9595,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9637,12 +9649,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9727,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9769,12 +9781,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9859,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9901,12 +9913,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9991,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10033,12 +10045,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10123,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -10165,12 +10177,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10255,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10297,12 +10309,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10387,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10429,12 +10441,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10519,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10561,12 +10573,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10651,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10693,12 +10705,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10783,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10825,12 +10837,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10915,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10957,12 +10969,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11047,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -11089,12 +11101,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11179,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -11221,12 +11233,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11343,12 +11355,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11433,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11475,12 +11487,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11565,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11607,12 +11619,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11729,12 +11741,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11819,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11861,12 +11873,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -11939,7 +11951,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11993,12 +12005,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12083,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -12125,12 +12137,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12215,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -12257,12 +12269,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12335,7 +12347,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12389,12 +12401,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12479,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12521,12 +12533,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12611,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12653,12 +12665,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12743,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12785,12 +12797,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12875,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12917,12 +12929,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -12995,7 +13007,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -13049,12 +13061,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13127,7 +13139,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -13181,12 +13193,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13271,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -13313,12 +13325,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13403,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13445,12 +13457,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13535,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13577,12 +13589,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13709,12 +13721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13799,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13841,12 +13853,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13931,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13973,12 +13985,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14095,12 +14107,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14185,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -14227,12 +14239,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14317,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14359,12 +14371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14449,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14491,12 +14503,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14569,7 +14581,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14623,12 +14635,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14713,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14755,12 +14767,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14845,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14887,12 +14899,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14977,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -15019,12 +15031,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15109,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -15151,12 +15163,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15241,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -15283,12 +15295,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15361,7 +15373,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15415,12 +15427,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15505,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15547,12 +15559,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15637,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15679,12 +15691,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15769,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15811,12 +15823,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15901,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15943,12 +15955,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16033,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -16075,12 +16087,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16165,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -16207,12 +16219,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16285,7 +16297,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -16339,12 +16351,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16429,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16471,12 +16483,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16561,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16603,12 +16615,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16693,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16735,12 +16747,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16813,7 +16825,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16867,12 +16879,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16957,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16999,12 +17011,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17089,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -17131,12 +17143,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17221,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -17263,12 +17275,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17341,7 +17353,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -17395,12 +17407,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17485,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17527,12 +17539,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17605,7 +17617,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17659,12 +17671,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17749,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17791,12 +17803,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -17869,7 +17881,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17923,12 +17935,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18001,7 +18013,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -18055,12 +18067,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18145,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -18187,12 +18199,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18265,7 +18277,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -18319,12 +18331,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:53Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18397,7 +18409,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -18451,12 +18463,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18541,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18583,12 +18595,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18661,7 +18673,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18715,12 +18727,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>
@@ -18793,7 +18805,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18847,12 +18859,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-16T12:40:52Z</t>
+          <t>2026-10-17T10:41:34Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:07</t>
+          <t>2026-10-17 10:41:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -586,11 +586,7 @@
           <t>R7233 032</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GW-R7233-032</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>SAMIYA MUSTAFA</t>
@@ -639,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -693,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -718,11 +714,7 @@
           <t>R7088 348</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GW-R7088-348</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>DAVIDSON TAWANA L</t>
@@ -771,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -825,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -850,11 +842,7 @@
           <t>R7026 283</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GW-R7026-283</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>MINTON EVELYN TICE</t>
@@ -903,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -957,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -982,11 +970,7 @@
           <t>18 158 09 007</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DK-18-158-09-007</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>DENNIS N HAROLD ESTATE</t>
@@ -1035,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1089,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1098,7 @@
           <t>18 319 05 030</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DK-18-319-05-030</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>PATTI MURR CARRERAS</t>
@@ -1167,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1221,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1246,11 +1226,7 @@
           <t>R6226 086</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GW-R6226-086</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>RIDING WILLIAM S &amp; KIMA S</t>
@@ -1299,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1353,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1378,11 +1354,7 @@
           <t>18 099 04 011</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DK-18-099-04-011</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>WILLIAM H ALSABROOK ESTATE</t>
@@ -1431,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1485,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1510,11 +1482,7 @@
           <t>18 106 13 058</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DK-18-106-13-058</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>DAVID E. AND MARK H SCHMITT</t>
@@ -1563,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1617,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1642,11 +1610,7 @@
           <t>18 299 19 133</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DK-18-299-19-133</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>PASHA CONNELL</t>
@@ -1695,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1749,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1774,11 +1738,7 @@
           <t>18 015 06 061</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DK-18-015-06-061</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>ELIZABETH BIZUNCH</t>
@@ -1827,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1881,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1906,11 +1866,7 @@
           <t>18 297 08 001</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DK-18-297-08-001</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>ANNE PETTIGREW ESTATE</t>
@@ -1959,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2013,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2038,11 +1994,7 @@
           <t>R6180D017</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GW-R6180D017</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>CAMERON ROBERT ALANSON ETAL</t>
@@ -2091,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2145,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2170,11 +2122,7 @@
           <t>18 038 07 016</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DK-18-038-07-016</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>GILBERTO MACHADO</t>
@@ -2223,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2277,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2302,11 +2250,7 @@
           <t>16 030 02 025</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>DK-16-030-02-025</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>VALERIE ELLISON ESTATE</t>
@@ -2355,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2409,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2434,11 +2378,7 @@
           <t>16 061 12 023</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DK-16-061-12-023</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>DEBORAH SOLTAU</t>
@@ -2487,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2541,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2566,11 +2506,7 @@
           <t>16 130 01 010</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DK-16-130-01-010</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>REESE GEORGE W EST PERS REP AND HEIRS REESE</t>
@@ -2619,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2673,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2698,11 +2634,7 @@
           <t>15 139 05 011</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DK-15-139-05-011</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>RALPH D DAVIS ESTATE</t>
@@ -2751,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2805,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2762,7 @@
           <t>18 291 08 054</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DK-18-291-08-054</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>NANCY JEAN BREWER</t>
@@ -2883,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2937,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2962,11 +2890,7 @@
           <t>18 141 15 003</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DK-18-141-15-003</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>LAURA A HONTGAS REVOCABLE LIVING TRUST HONTGAS</t>
@@ -3015,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3069,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3094,11 +3018,7 @@
           <t>15 062 03 011</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>DK-15-062-03-011</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>EDWARD A MCDONNELL ESTATE</t>
@@ -3147,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3201,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3226,11 +3146,7 @@
           <t>15 163 03 014</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DK-15-163-03-014</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>HUGH L RUTLEDGE &amp; JAMES K RUTLEDGE ESTATE</t>
@@ -3279,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3333,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3358,11 +3274,7 @@
           <t>16 104 06 040</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>DK-16-104-06-040</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>ABOGHANIM ABDURRHMAN ABDULLAH ABOGHANIM</t>
@@ -3411,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3465,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3490,11 +3402,7 @@
           <t>16 104 08 040</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>DK-16-104-08-040</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>DENISE JENKINS</t>
@@ -3543,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3597,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3622,11 +3530,7 @@
           <t>15 177 04 068</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>DK-15-177-04-068</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>CHARLOTTE B ZOTTI ESTATE</t>
@@ -3675,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3729,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3754,11 +3658,7 @@
           <t>15 132 03 027</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>DK-15-132-03-027</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>DEBBIE PACE</t>
@@ -3807,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3861,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3886,11 +3786,7 @@
           <t>15 184 03 019</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DK-15-184-03-019</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>LAVERNE OXENDINE JORDAN ESTATE</t>
@@ -3939,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3993,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4018,11 +3914,7 @@
           <t>R6246B123</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>GW-R6246B123</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>IRENE GUTIERREZ</t>
@@ -4071,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4125,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4150,11 +4042,7 @@
           <t>16 002 05 045</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>DK-16-002-05-045</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>REBECCA DARLENE STEPHENS</t>
@@ -4203,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4257,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4282,11 +4170,7 @@
           <t>15 253 04 031</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>DK-15-253-04-031</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>WALTER V LUBOVICK ESTATE</t>
@@ -4335,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4389,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4414,11 +4298,7 @@
           <t>15 089 05 008</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DK-15-089-05-008</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>HAMID BRICHI</t>
@@ -4467,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4521,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4426,7 @@
           <t>16 153 13 016</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DK-16-153-13-016</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>JERRY DOBBINS &amp; WANDA DOBBINS</t>
@@ -4599,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4653,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4678,11 +4554,7 @@
           <t>16 075 04 034</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>DK-16-075-04-034</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>MAXIME AND ALICE PAPILLON</t>
@@ -4731,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4785,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4810,11 +4682,7 @@
           <t>16 001 12 003</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>DK-16-001-12-003</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>DENISE A BREDEN</t>
@@ -4863,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4917,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4942,11 +4810,7 @@
           <t>18 092 08 025</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DK-18-092-08-025</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>DOROTHY JANE WITHERS</t>
@@ -4995,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5049,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5074,11 +4938,7 @@
           <t>18 044 09 034</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DK-18-044-09-034</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>ALVIN B MARBLE</t>
@@ -5127,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5181,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5206,11 +5066,7 @@
           <t>15 208 04 156</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>DK-15-208-04-156</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>GRAHAM HAY</t>
@@ -5259,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5313,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5338,11 +5194,7 @@
           <t>18 172 01 104</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DK-18-172-01-104</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>TOP DESIGNS GROUP</t>
@@ -5391,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5445,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5322,7 @@
           <t>18 074 05 019</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>DK-18-074-05-019</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>MYRTIS E PRUITT ESTATE</t>
@@ -5523,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5577,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5602,11 +5450,7 @@
           <t>16 152 04 001</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>DK-16-152-04-001</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>SHANIQUA CAULDWELL</t>
@@ -5655,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5709,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5734,11 +5578,7 @@
           <t>16 074 16 006</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DK-16-074-16-006</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>BEATRICE ANDREWS</t>
@@ -5787,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5841,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5866,11 +5706,7 @@
           <t>16 154 06 001</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DK-16-154-06-001</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>ROBERT ODELL HINES ESTATE &amp; LILLIE MAE BENNETT ESTATE</t>
@@ -5919,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5973,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5998,11 +5834,7 @@
           <t>R7044 075</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>GW-R7044-075</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>HAYES TIMOTHY L</t>
@@ -6095,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6120,11 +5952,7 @@
           <t>16 123 05 045</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>DK-16-123-05-045</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>STELLA M TAYLOR ESTATE</t>
@@ -6173,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6227,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6252,11 +6080,7 @@
           <t>R6321A014</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>GW-R6321A014</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>HOLCOMBE MARLON</t>
@@ -6349,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6374,11 +6198,7 @@
           <t>15 220 09 014</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>DK-15-220-09-014</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>BRETT MULLINS</t>
@@ -6427,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6481,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6506,11 +6326,7 @@
           <t>16 009 02 036</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DK-16-009-02-036</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>BOYD BROOKS &amp; LAKEMBA WARD</t>
@@ -6559,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6613,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6454,7 @@
           <t>R7259 221</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>GW-R7259-221</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>LAND BUFORD HWY</t>
@@ -6691,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6745,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6770,11 +6582,7 @@
           <t>R7252 031</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>GW-R7252-031</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>PEACHTREE/SUWANEE</t>
@@ -6823,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6877,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6902,11 +6710,7 @@
           <t>15 229 05 019</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>DK-15-229-05-019</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>CATALINA</t>
@@ -6955,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7009,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7034,11 +6838,7 @@
           <t>R7093 009A</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>GW-R7093-009A</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>SUNNY HILL HOME DEMON</t>
@@ -7087,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -7141,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7166,11 +6966,7 @@
           <t>18 013 06 001</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DK-18-013-06-001</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>OSCAR O HERNANDEZ PADILLA</t>
@@ -7219,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7273,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7298,11 +7094,7 @@
           <t>R6154 562</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>GW-R6154-562</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>OAKTREE</t>
@@ -7351,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7405,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7222,7 @@
           <t>16 153 08 047</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>DK-16-153-08-047</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>BRENDA PHILPOT</t>
@@ -7483,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7537,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7562,11 +7350,7 @@
           <t>18 309 07 038</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>DK-18-309-07-038</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>NICK LONG JR ESTATE</t>
@@ -7615,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7669,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7694,11 +7478,7 @@
           <t>16 074 07 024</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>DK-16-074-07-024</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>BRETT O MULLINGS</t>
@@ -7747,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7801,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7826,11 +7606,7 @@
           <t>16 074 08 085</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-085</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>NATHAN SMITH &amp; STEVEN HAMMOND &amp; DELITA D. PERRINO</t>
@@ -7879,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7933,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7958,11 +7734,7 @@
           <t>15 090 06 039</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>DK-15-090-06-039</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>DREAM ILLUMINATION FOUNDATION</t>
@@ -8011,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -8065,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8090,11 +7862,7 @@
           <t>16 152 11 020</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>DK-16-152-11-020</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>CALVIN CHAN</t>
@@ -8143,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -8197,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8222,11 +7990,7 @@
           <t>16 074 08 083</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-083</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>NATHAN SMITH &amp; STEVEN HAMMOND &amp; LIANE TRUELL</t>
@@ -8275,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8329,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8354,11 +8118,7 @@
           <t>16 141 02 013</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>DK-16-141-02-013</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>DONOVAN SQUIRES</t>
@@ -8407,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8461,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8486,11 +8246,7 @@
           <t>16 074 08 095</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-095</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>NATHAN SMITH &amp; MARY ELIZABETH HIRSCH</t>
@@ -8539,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8593,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8618,11 +8374,7 @@
           <t>15 193 04 026</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>DK-15-193-04-026</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>AKIM RAVARIERE &amp; MELINA RAVARIERE</t>
@@ -8671,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8725,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8750,11 +8502,7 @@
           <t>15 181 05 018</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>DK-15-181-05-018</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>ZION TASHKENT TASHKENT</t>
@@ -8803,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8857,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8882,11 +8630,7 @@
           <t>15 101 01 005</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>DK-15-101-01-005</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>STEVEN EDWARD BRIEN</t>
@@ -8935,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8989,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9014,11 +8758,7 @@
           <t>18 224 01 020</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>DK-18-224-01-020</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>NOAH DOSS</t>
@@ -9067,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -9121,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9146,11 +8886,7 @@
           <t>18 046 03 070</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-070</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>MOSELY FREDRICK HIS ESTATE PERS REP AND HEIRS KNOWN AND UNKNOWN</t>
@@ -9199,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -9253,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9278,11 +9014,7 @@
           <t>16 153 08 006</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>DK-16-153-08-006</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>RHONEIA N STARKS</t>
@@ -9331,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9385,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9410,11 +9142,7 @@
           <t>15 093 07 006</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>DK-15-093-07-006</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>U S HOUSING &amp; URBAN DEV</t>
@@ -9463,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9517,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9542,11 +9270,7 @@
           <t>18 341 10 001</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>DK-18-341-10-001</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>DAVID CHESTNUT</t>
@@ -9595,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9649,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9674,11 +9398,7 @@
           <t>16 074 08 092</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-092</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>PATRICIA ANN MARSHALL</t>
@@ -9727,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9781,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9806,11 +9526,7 @@
           <t>R5005 149</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>GW-R5005-149</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>WEIDLICH</t>
@@ -9859,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9913,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9938,11 +9654,7 @@
           <t>16 074 07 016</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>DK-16-074-07-016</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>TOSHA DEACON</t>
@@ -9991,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -10045,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10070,11 +9782,7 @@
           <t>R7266 232</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>GW-R7266-232</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>ARONSON</t>
@@ -10123,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -10177,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10202,11 +9910,7 @@
           <t>R4346A168</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>GW-R4346A168</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>DENSON</t>
@@ -10255,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10309,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10334,11 +10038,7 @@
           <t>18 046 03 087</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-087</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>SCOTT JOHN GILBERT</t>
@@ -10387,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10441,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10466,11 +10166,7 @@
           <t>15 090 07 013</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>DK-15-090-07-013</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>RODRIGUEZ MARTA GRANDA LIVING RODRIGUEZ MARTA G</t>
@@ -10519,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10573,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10598,11 +10294,7 @@
           <t>R7305 083</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>GW-R7305-083</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>GARMON EVERETT E ETAL</t>
@@ -10651,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10705,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10730,11 +10422,7 @@
           <t>R6058 137</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>GW-R6058-137</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>JERE M.</t>
@@ -10783,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10837,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10862,11 +10550,7 @@
           <t>R6281 018</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>GW-R6281-018</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>BAY COLONY PROPERTY CO JONES MILL RD</t>
@@ -10915,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10969,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10994,11 +10678,7 @@
           <t>18 126 15 012</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>DK-18-126-15-012</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>ROSA REID ESTATE</t>
@@ -11047,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -11101,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11126,11 +10806,7 @@
           <t>18 015 06 013</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>DK-18-015-06-013</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>A AND A INVESTMENT AND</t>
@@ -11179,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -11233,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11258,11 +10934,7 @@
           <t>R6109 102</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>GW-R6109-102</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>COOK</t>
@@ -11355,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11380,11 +11052,7 @@
           <t>R6095 088</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>GW-R6095-088</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>CRUSSELLE</t>
@@ -11433,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11487,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11512,11 +11180,7 @@
           <t>15 192 02 010</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>DK-15-192-02-010</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>ELVIA PELAYO</t>
@@ -11565,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11619,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11644,11 +11308,7 @@
           <t>R4346A247</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>GW-R4346A247</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>BENJAMIN</t>
@@ -11741,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11766,11 +11426,7 @@
           <t>16 046 01 098</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>DK-16-046-01-098</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>ANNMARIE PLUMMER-BAILEY</t>
@@ -11819,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11873,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11898,11 +11554,7 @@
           <t>18 068 11 027</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>DK-18-068-11-027</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>ABDULKADIR AHMED</t>
@@ -11951,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -12005,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12030,11 +11682,7 @@
           <t>R4348A062</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>GW-R4348A062</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>MARY</t>
@@ -12083,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -12137,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12162,11 +11810,7 @@
           <t>16 218 03 082</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>DK-16-218-03-082</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>MICHAEL BOWMAN</t>
@@ -12215,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -12269,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12294,11 +11938,7 @@
           <t>18 047 23 022</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>DK-18-047-23-022</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>MARY ANN EDWARDS ESTATE</t>
@@ -12347,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12401,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12426,11 +12066,7 @@
           <t>R6067 098</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>GW-R6067-098</t>
-        </is>
-      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>BUTSCH</t>
@@ -12479,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12533,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12558,11 +12194,7 @@
           <t>18 044 09 059</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>DK-18-044-09-059</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>JIMMY L JACKSON &amp; MABLE MCWHORTER JACKSON</t>
@@ -12611,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12665,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12690,11 +12322,7 @@
           <t>15 096 02 121</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>DK-15-096-02-121</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>CECIL DAVIS ESTATE</t>
@@ -12743,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12797,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12822,11 +12450,7 @@
           <t>15 027 01 090</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>DK-15-027-01-090</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>RIVER MILL ROCK MILL CLUB MILL</t>
@@ -12875,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12929,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12954,11 +12578,7 @@
           <t>18 044 09 080</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>DK-18-044-09-080</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>CHARLES E ANDERSON ESTATE</t>
@@ -13007,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -13061,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13086,11 +12706,7 @@
           <t>18 073 01 161</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>DK-18-073-01-161</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>SABRINA YOUNG</t>
@@ -13139,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -13193,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13218,11 +12834,7 @@
           <t>18 004 17 061</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>DK-18-004-17-061</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>HOWARD TOMMY EUGENE HOWARD MARY LEE</t>
@@ -13271,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -13325,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13350,11 +12962,7 @@
           <t>R6276 022</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>GW-R6276-022</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>BAY COLONY PROPERTY CO JONES MILL CT</t>
@@ -13403,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13457,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13482,11 +13090,7 @@
           <t>15 156 03 001</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>DK-15-156-03-001</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>YARED BEEWKETU KASEG</t>
@@ -13535,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13589,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13614,11 +13218,7 @@
           <t>18 225 02 003</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>DK-18-225-02-003</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>CHANEREE THIEN</t>
@@ -13667,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13721,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13746,11 +13346,7 @@
           <t>R6128 123</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>GW-R6128-123</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>BRENTWOOD-GLOSTER</t>
@@ -13799,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13853,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13878,11 +13474,7 @@
           <t>16 074 14 029</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>DK-16-074-14-029</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>JERMAINE PREDESTIN &amp; REGINA MENDEZ</t>
@@ -13931,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13985,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14010,11 +13602,7 @@
           <t>R5140 189</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>GW-R5140-189</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>SIBLEY</t>
@@ -14107,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14132,11 +13720,7 @@
           <t>18 187 01 246</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>DK-18-187-01-246</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>C.O. EDWARDS &amp; CARL M. CAIN</t>
@@ -14185,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -14239,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14264,11 +13848,7 @@
           <t>16 137 08 011</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>DK-16-137-08-011</t>
-        </is>
-      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>NANCY L KENNEDY</t>
@@ -14317,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -14371,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14396,11 +13976,7 @@
           <t>18 046 03 106</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-106</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>CRONAN BROTHERS</t>
@@ -14449,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14503,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14528,11 +14104,7 @@
           <t>R4348A061</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>GW-R4348A061</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>MARY</t>
@@ -14581,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14635,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14660,11 +14232,7 @@
           <t>16 043 03 078</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>DK-16-043-03-078</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>WILLIAM H ROBINSON JR ESTATE</t>
@@ -14713,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14767,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14792,11 +14360,7 @@
           <t>18 046 03 060</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-060</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>GWENDOLYN HEATH ESTATE</t>
@@ -14845,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14899,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14924,11 +14488,7 @@
           <t>18 018 01 121</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>DK-18-018-01-121</t>
-        </is>
-      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>MONICA BOBB BOWMAN</t>
@@ -14977,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -15031,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15056,11 +14616,7 @@
           <t>18 046 03 093</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-093</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>UNKNOWN OWNER - UNRETURNED PROPERTY</t>
@@ -15109,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -15163,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15188,11 +14744,7 @@
           <t>18 046 03 051</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-051</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>ALICE WATKINS</t>
@@ -15241,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -15295,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15320,11 +14872,7 @@
           <t>18 046 03 211</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-211</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>BOYD MARIE HER ESTATE ADMINISTRATOR EXECUTOR AND HEIRS KNOWN AND UNKNOWN</t>
@@ -15373,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -15427,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15452,11 +15000,7 @@
           <t>18 046 03 069</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-069</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>MARY M MATTHEWS</t>
@@ -15505,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15559,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15584,11 +15128,7 @@
           <t>16 140 02 012</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>DK-16-140-02-012</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>WILLIAM H. BROOKS ESTATE</t>
@@ -15637,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15691,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15716,11 +15256,7 @@
           <t>18 046 03 037</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-037</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>JAMES GRESHAM</t>
@@ -15769,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15823,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15848,11 +15384,7 @@
           <t>18 046 03 236</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-236</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>GALLOWAY JAMES ESTATE PERS REP AND HEIRS KNOWN AND UNKNOWN</t>
@@ -15901,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15955,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15980,11 +15512,7 @@
           <t>18 047 26 017</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>DK-18-047-26-017</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>MARY EMILY &amp; SURVARIA BREWER ESTATES</t>
@@ -16033,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -16087,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16112,11 +15640,7 @@
           <t>R6154 569</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>GW-R6154-569</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>OAKTREE</t>
@@ -16165,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -16219,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16244,11 +15768,7 @@
           <t>R6183 166</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>GW-R6183-166</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>HICKORY</t>
@@ -16297,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -16351,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16376,11 +15896,7 @@
           <t>15 199 04 193</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>DK-15-199-04-193</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>GETHSEMANE TEMPLE AFFILIATED WITH UHC</t>
@@ -16429,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -16483,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16508,11 +16024,7 @@
           <t>18 203 06 069</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>DK-18-203-06-069</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>MCJENKIN ESTHER H MRS</t>
@@ -16561,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16615,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16640,11 +16152,7 @@
           <t>18 046 03 067</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-067</t>
-        </is>
-      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>UNKNOWN OWNER - UNRETURNED PROPERTY 3180 altacrest dr SCOTTDALE 30079</t>
@@ -16693,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16747,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16772,11 +16280,7 @@
           <t>18 081 05 073</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>DK-18-081-05-073</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>ANNMARIE PLUMMER BAILEY &amp; WINSTON BAILEY</t>
@@ -16825,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16879,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16904,11 +16408,7 @@
           <t>R7069 420</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>GW-R7069-420</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>STERLING</t>
@@ -16957,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -17011,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17036,11 +16536,7 @@
           <t>15 122 06 066</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>DK-15-122-06-066</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>EDGAR DUNCAN</t>
@@ -17089,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -17143,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17168,11 +16664,7 @@
           <t>18 046 03 011</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>DK-18-046-03-011</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>FRED WILLIAMS ESTATE</t>
@@ -17221,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -17275,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17300,11 +16792,7 @@
           <t>R6120 107</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>GW-R6120-107</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>W W BUILDERS</t>
@@ -17353,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -17407,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17432,11 +16920,7 @@
           <t>18 047 23 016</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>DK-18-047-23-016</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>BROWN JOHNSON</t>
@@ -17485,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17539,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17564,11 +17048,7 @@
           <t>15 058 05 035</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>DK-15-058-05-035</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>LEROY HARDING 3289 BLAZING PINE KNL #A DECATUR 30034</t>
@@ -17617,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17671,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17696,11 +17176,7 @@
           <t>18 225 03 022</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>DK-18-225-03-022</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>P D HOPKINS</t>
@@ -17749,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17803,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17828,11 +17304,7 @@
           <t>R6114 027</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>GW-R6114-027</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>CELESTINO MACEDO-JAMES</t>
@@ -17881,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17935,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17960,11 +17432,7 @@
           <t>R5137 171</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>GW-R5137-171</t>
-        </is>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>BP DIVERSIFIED ASSETS GROUP</t>
@@ -18013,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -18067,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18092,11 +17560,7 @@
           <t>16 074 08 101</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>DK-16-074-08-101</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>ETHEL J MABRY ESTATE</t>
@@ -18145,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -18199,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18224,11 +17688,7 @@
           <t>R4349 085</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>GW-R4349-085</t>
-        </is>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>ELITE</t>
@@ -18277,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -18331,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:47Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18356,11 +17816,7 @@
           <t>15 174 08 067</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>DK-15-174-08-067</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>W C ELLINGTON</t>
@@ -18409,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -18463,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18488,11 +17944,7 @@
           <t>16 009 02 005</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>DK-16-009-02-005</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>ROSE BURNEY</t>
@@ -18541,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18595,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18620,11 +18072,7 @@
           <t>15 191 01 108</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>DK-15-191-01-108</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>BRUCE T HANSEN</t>
@@ -18673,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18727,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18752,11 +18200,7 @@
           <t>16 169 07 061</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>DK-16-169-07-061</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>TOMMIE ABBOTT</t>
@@ -18805,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18859,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:34Z</t>
+          <t>2026-10-18T11:01:46Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:47Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:46Z</t>
+          <t>2026-10-19T13:10:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:38Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-21T11:46:18Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +689,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +6941,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +8093,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +8221,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +8733,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +10525,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11027,12 +11027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +11283,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +11529,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +11913,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12243,7 +12243,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +12297,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +12937,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +13065,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +13321,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13695,12 +13695,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +13951,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +14079,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +14207,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +14335,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +14463,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +15103,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15433,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +15487,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +15615,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +15743,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +15871,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +15999,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +16127,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +16255,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +16383,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +16511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16585,7 +16585,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-46</v>
+        <v>-45</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +16767,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +16895,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +17023,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17097,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +17151,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +17407,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +17663,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17737,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +17791,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +18047,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +18175,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:18Z</t>
+          <t>2026-10-20T11:33:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB140"/>
+  <dimension ref="A1:AF140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,26 @@
           <t>Enriched_Timestamp</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Owner_Name_Redacted</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>docket_id</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>parcel_id_raw</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Access_Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -586,10 +606,14 @@
           <t>R7233 032</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Parcel R723████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SAMIYA MUSTAFA</t>
+          <t>S. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -605,7 +629,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3920 WESTBROOK RD, Gwinnett County, GA</t>
+          <t>3920 WESTBROOK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -635,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -689,12 +713,32 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>S. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>R7233 032</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>R7233 032</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -714,10 +758,14 @@
           <t>R7088 348</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Parcel R708████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DAVIDSON TAWANA L</t>
+          <t>D. &amp; T. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -733,7 +781,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1870 SPRING ROSE GLN, Gwinnett County, GA</t>
+          <t>1870 SPRING [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -763,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -817,12 +865,32 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>D. &amp; T. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>R7088 348</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>R7088 348</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -842,10 +910,14 @@
           <t>R7026 283</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Parcel R702████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MINTON EVELYN TICE</t>
+          <t>M. &amp; E. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -861,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1040 SUNNY FIELD CT, Gwinnett County, GA</t>
+          <t>1040 SUNNY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -891,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -945,12 +1017,32 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>M. &amp; E. T████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>R7026 283</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>R7026 283</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -970,10 +1062,14 @@
           <t>18 158 09 007</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Parcel 18 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DENNIS N HAROLD ESTATE</t>
+          <t>D. &amp; N. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -989,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1902 INNWOOD RD NE, Atlanta, GA 30329</t>
+          <t>1902 INNWOOD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1019,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1073,12 +1169,32 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>D. &amp; N. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>18 158 09 007</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>18 158 09 007</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1098,10 +1214,14 @@
           <t>18 319 05 030</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parcel 18 3████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PATTI MURR CARRERAS</t>
+          <t>P. &amp; M. C███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1117,7 +1237,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3885 WATEROAK WAY, Atlanta, GA 30340</t>
+          <t>3885 WATEROAK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1147,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1201,12 +1321,32 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>P. &amp; M. C███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>18 319 05 030</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>18 319 05 030</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1226,10 +1366,14 @@
           <t>R6226 086</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Parcel R622████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RIDING WILLIAM S &amp; KIMA S</t>
+          <t>R. &amp; W. S████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1245,7 +1389,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2212 TAHOE CT, Gwinnett County, GA</t>
+          <t>2212 TAHOE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1275,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1329,12 +1473,32 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>R. &amp; W. S████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>R6226 086</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>R6226 086</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1518,14 @@
           <t>18 099 04 011</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WILLIAM H ALSABROOK ESTATE</t>
+          <t>W. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1373,7 +1541,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>924 BROOKDALE PL, Decatur, GA 30033</t>
+          <t>924 BROOKDALE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1457,12 +1625,32 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>W. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>18 099 04 011</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>18 099 04 011</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1482,10 +1670,14 @@
           <t>18 106 13 058</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Parcel 18 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DAVID E. AND MARK H SCHMITT</t>
+          <t>D. &amp; E. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1501,7 +1693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1276 WEATHERSTONE DR NE, Atlanta, GA 30324</t>
+          <t>1276 WEATHERSTONE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1585,12 +1777,32 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>D. &amp; E. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>18 106 13 058</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>18 106 13 058</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1610,10 +1822,14 @@
           <t>18 299 19 133</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PASHA CONNELL</t>
+          <t>P. &amp; C. C██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1629,7 +1845,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5300 PEACHTREE RD 3607, Chamblee, GA 30341</t>
+          <t>5300 PEACHTREE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1659,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1713,12 +1929,32 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>P. &amp; C. C██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>18 299 19 133</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>18 299 19 133</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1738,10 +1974,14 @@
           <t>18 015 06 061</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ELIZABETH BIZUNCH</t>
+          <t>E. &amp; B. B██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1757,7 +1997,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>605 ALLGOOD RD, Stone Mountain, GA 30083</t>
+          <t>605 ALLGOOD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1787,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1841,12 +2081,32 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>E. &amp; B. B██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>18 015 06 061</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>18 015 06 061</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1866,10 +2126,14 @@
           <t>18 297 08 001</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANNE PETTIGREW ESTATE</t>
+          <t>A. &amp; P. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1885,7 +2149,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2537 STAFFORD PL, Atlanta, GA 30340</t>
+          <t>2537 STAFFORD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1915,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1969,12 +2233,32 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>A. &amp; P. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>18 297 08 001</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>18 297 08 001</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -1994,10 +2278,14 @@
           <t>R6180D017</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Parcel R618████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CAMERON ROBERT ALANSON ETAL</t>
+          <t>C. &amp; R. E████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2013,7 +2301,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1219 OVERTON DR, Gwinnett County, GA</t>
+          <t>1219 OVERTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2043,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2097,12 +2385,32 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>C. &amp; R. E████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>R6180D017</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>R6180D017</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2122,10 +2430,14 @@
           <t>18 038 07 016</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GILBERTO MACHADO</t>
+          <t>G. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2141,7 +2453,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>356 DERBYSHIRE DR, Stone Mountain, GA 30088</t>
+          <t>356 DERBYSHIRE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2171,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2225,12 +2537,32 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>G. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>18 038 07 016</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>18 038 07 016</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2250,10 +2582,14 @@
           <t>16 030 02 025</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VALERIE ELLISON ESTATE</t>
+          <t>V. &amp; E. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2269,7 +2605,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1360 HIDDEN HILLS PKWY, Stone Mountain, GA 30088</t>
+          <t>1360 HIDDEN [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2299,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2353,12 +2689,32 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>V. &amp; E. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>16 030 02 025</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>16 030 02 025</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2378,10 +2734,14 @@
           <t>16 061 12 023</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DEBORAH SOLTAU</t>
+          <t>D. &amp; S. S█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2397,7 +2757,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1528 STONELEIGH CIRCLE, Stone Mountain, GA 30088</t>
+          <t>1528 STONELEIGH [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2427,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2481,12 +2841,32 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>D. &amp; S. S█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>16 061 12 023</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>16 061 12 023</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2886,14 @@
           <t>16 130 01 010</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>REESE GEORGE W EST PERS REP AND HEIRS REESE</t>
+          <t>R. &amp; G. R████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2525,7 +2909,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1131 S DESHON RD, Lithonia, GA 30058</t>
+          <t>1131 S [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2555,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2609,12 +2993,32 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>R. &amp; G. R████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>16 130 01 010</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>16 130 01 010</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2634,10 +3038,14 @@
           <t>15 139 05 011</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RALPH D DAVIS ESTATE</t>
+          <t>R. &amp; D. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2653,7 +3061,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2411 CRANBROOKE DR, Decatur, GA 30032</t>
+          <t>2411 CRANBROOKE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2683,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2737,12 +3145,32 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>R. &amp; D. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>15 139 05 011</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>15 139 05 011</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2762,10 +3190,14 @@
           <t>18 291 08 054</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NANCY JEAN BREWER</t>
+          <t>N. &amp; J. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2781,7 +3213,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4053 WOODRIDGE WAY, Tucker, GA 30084</t>
+          <t>4053 WOODRIDGE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2811,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2865,12 +3297,32 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>N. &amp; J. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>18 291 08 054</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>18 291 08 054</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -2890,10 +3342,14 @@
           <t>18 141 15 003</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Parcel 18 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LAURA A HONTGAS REVOCABLE LIVING TRUST HONTGAS</t>
+          <t>L. &amp; A. H██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2909,7 +3365,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1374 ORCHARD PARK DR, Stone Mountain, GA 30083</t>
+          <t>1374 ORCHARD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2939,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2993,12 +3449,32 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>L. &amp; A. H██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>18 141 15 003</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>18 141 15 003</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3018,10 +3494,14 @@
           <t>15 062 03 011</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EDWARD A MCDONNELL ESTATE</t>
+          <t>E. &amp; A. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3037,7 +3517,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3625 RADCLIFFE BLVD, Decatur, GA 30034</t>
+          <t>3625 RADCLIFFE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3067,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3121,12 +3601,32 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>E. &amp; A. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>15 062 03 011</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>15 062 03 011</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3646,14 @@
           <t>15 163 03 014</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HUGH L RUTLEDGE &amp; JAMES K RUTLEDGE ESTATE</t>
+          <t>H. &amp; L. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3165,7 +3669,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4185 HANES DR, Decatur, GA 30035</t>
+          <t>4185 HANES [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3195,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3249,12 +3753,32 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>H. &amp; L. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>15 163 03 014</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>15 163 03 014</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3274,10 +3798,14 @@
           <t>16 104 06 040</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ABOGHANIM ABDURRHMAN ABDULLAH ABOGHANIM</t>
+          <t>A. &amp; A. A████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3293,7 +3821,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2176 WELLINGTON CIR, Lithonia, GA 30058</t>
+          <t>2176 WELLINGTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3323,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3377,12 +3905,32 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>A. &amp; A. A████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>16 104 06 040</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>16 104 06 040</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3402,10 +3950,14 @@
           <t>16 104 08 040</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DENISE JENKINS</t>
+          <t>D. &amp; J. J██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3421,7 +3973,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6348 WELLINGTON WALK WAY, Lithonia, GA 30058</t>
+          <t>6348 WELLINGTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3451,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3505,12 +4057,32 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>D. &amp; J. J██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>16 104 08 040</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>16 104 08 040</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3530,10 +4102,14 @@
           <t>15 177 04 068</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CHARLOTTE B ZOTTI ESTATE</t>
+          <t>C. &amp; B. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3549,7 +4125,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1240 MCPHERSON AVE, Atlanta, GA 30316</t>
+          <t>1240 MCPHERSON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3579,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3633,12 +4209,32 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>C. &amp; B. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>15 177 04 068</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>15 177 04 068</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3658,10 +4254,14 @@
           <t>15 132 03 027</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DEBBIE PACE</t>
+          <t>D. &amp; P. P████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3677,7 +4277,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2397 TIFFANY PLACE, Decatur, GA 30035</t>
+          <t>2397 TIFFANY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3707,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3761,12 +4361,32 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>D. &amp; P. P████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>15 132 03 027</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>15 132 03 027</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3786,10 +4406,14 @@
           <t>15 184 03 019</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LAVERNE OXENDINE JORDAN ESTATE</t>
+          <t>L. &amp; O. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3805,7 +4429,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2719 AMELIA AVE, Decatur, GA 30032</t>
+          <t>2719 AMELIA [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3835,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3889,12 +4513,32 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>L. &amp; O. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>15 184 03 019</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>15 184 03 019</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -3914,10 +4558,14 @@
           <t>R6246B123</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Parcel R624████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IRENE GUTIERREZ</t>
+          <t>I. &amp; G. G████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3933,7 +4581,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6204 JANE RD, Gwinnett County, GA</t>
+          <t>6204 JANE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3963,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4017,12 +4665,32 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I. &amp; G. G████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>R6246B123</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>R6246B123</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4042,10 +4710,14 @@
           <t>16 002 05 045</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>REBECCA DARLENE STEPHENS</t>
+          <t>R. &amp; D. S███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4061,7 +4733,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1121 VILLAGE MAIN ST, Stone Mountain, GA 30088</t>
+          <t>1121 VILLAGE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4091,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4145,12 +4817,32 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>R. &amp; D. S███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>16 002 05 045</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>16 002 05 045</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4170,10 +4862,14 @@
           <t>15 253 04 031</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Parcel 15 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>WALTER V LUBOVICK ESTATE</t>
+          <t>W. &amp; V. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4189,7 +4885,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4000 SEVEN HILLS TRAIL, Stone Mountain, GA 30083</t>
+          <t>4000 SEVEN [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4219,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4273,12 +4969,32 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>W. &amp; V. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>15 253 04 031</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>15 253 04 031</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4298,10 +5014,14 @@
           <t>15 089 05 008</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HAMID BRICHI</t>
+          <t>H. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4317,7 +5037,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3213 PANTHERS TRACE, Decatur, GA 30034</t>
+          <t>3213 PANTHERS [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4347,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4401,12 +5121,32 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>H. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>15 089 05 008</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>15 089 05 008</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4426,10 +5166,14 @@
           <t>16 153 13 016</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>JERRY DOBBINS &amp; WANDA DOBBINS</t>
+          <t>J. &amp; D. D██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4445,7 +5189,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2707 ROCK CHAPEL RD, Lithonia, GA 30058</t>
+          <t>2707 ROCK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4475,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -4529,12 +5273,32 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>J. &amp; D. D██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>16 153 13 016</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>16 153 13 016</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4554,10 +5318,14 @@
           <t>16 075 04 034</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MAXIME AND ALICE PAPILLON</t>
+          <t>M. &amp; A. P███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4573,7 +5341,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5824 PAR FOUR CT, Lithonia, GA 30038</t>
+          <t>5824 PAR [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4603,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -4657,12 +5425,32 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>M. &amp; A. P███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>16 075 04 034</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>16 075 04 034</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4682,10 +5470,14 @@
           <t>16 001 12 003</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DENISE A BREDEN</t>
+          <t>D. &amp; A. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4701,7 +5493,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>885 DISNEY CT, Stone Mountain, GA 30088</t>
+          <t>885 DISNEY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4731,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -4785,12 +5577,32 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>D. &amp; A. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>16 001 12 003</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>16 001 12 003</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4810,10 +5622,14 @@
           <t>18 092 08 025</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DOROTHY JANE WITHERS</t>
+          <t>D. &amp; J. W██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4829,7 +5645,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>913 PARK GATE PL, Stone Mountain, GA 30083</t>
+          <t>913 PARK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4859,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -4913,12 +5729,32 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>D. &amp; J. W██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>18 092 08 025</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>18 092 08 025</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -4938,10 +5774,14 @@
           <t>18 044 09 034</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALVIN B MARBLE</t>
+          <t>A. &amp; B. M█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4957,7 +5797,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>615 RIDGECREEK DR, Clarkston, GA 30021</t>
+          <t>615 RIDGECREEK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4987,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5041,12 +5881,32 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>A. &amp; B. M█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>18 044 09 034</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>18 044 09 034</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5066,10 +5926,14 @@
           <t>15 208 04 156</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Parcel 15 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GRAHAM HAY</t>
+          <t>G. &amp; H. H████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5085,7 +5949,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1237 WYLIE ST, Atlanta, GA 30317</t>
+          <t>1237 WYLIE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5115,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -5169,12 +6033,32 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>G. &amp; H. H████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>15 208 04 156</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>15 208 04 156</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5194,10 +6078,14 @@
           <t>18 172 01 104</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Parcel 18 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TOP DESIGNS GROUP</t>
+          <t>T. &amp; D. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5213,7 +6101,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5191 MOUNTAIN SHADOW LN, Stone Mountain, GA 30087</t>
+          <t>5191 MOUNTAIN [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5243,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -5297,12 +6185,32 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>T. &amp; D. G████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>18 172 01 104</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>18 172 01 104</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5322,10 +6230,14 @@
           <t>18 074 05 019</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MYRTIS E PRUITT ESTATE</t>
+          <t>M. &amp; E. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5341,7 +6253,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5441 MASON LANE, Stone Mountain, GA 30083</t>
+          <t>5441 MASON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5371,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -5425,12 +6337,32 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>M. &amp; E. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>18 074 05 019</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>18 074 05 019</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5450,10 +6382,14 @@
           <t>16 152 04 001</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SHANIQUA CAULDWELL</t>
+          <t>S. &amp; C. C████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5469,7 +6405,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6901 MAGNOLIA STREET, Lithonia, GA 30058</t>
+          <t>6901 MAGNOLIA [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5499,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -5553,12 +6489,32 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>S. &amp; C. C████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>16 152 04 001</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>16 152 04 001</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5578,10 +6534,14 @@
           <t>16 074 16 006</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BEATRICE ANDREWS</t>
+          <t>B. &amp; A. A██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5597,7 +6557,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1201 FAIRINGTON RIDGE CIR, Lithonia, GA 30038</t>
+          <t>1201 FAIRINGTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5627,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -5681,12 +6641,32 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>B. &amp; A. A██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>16 074 16 006</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>16 074 16 006</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5706,10 +6686,14 @@
           <t>16 154 06 001</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ROBERT ODELL HINES ESTATE &amp; LILLIE MAE BENNETT ESTATE</t>
+          <t>R. &amp; O. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5725,7 +6709,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7056 PINE MOUNTAIN RD, Lithonia, GA 30058</t>
+          <t>7056 PINE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5755,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -5809,12 +6793,32 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>R. &amp; O. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>16 154 06 001</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>16 154 06 001</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5834,10 +6838,14 @@
           <t>R7044 075</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Parcel R704████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HAYES TIMOTHY L</t>
+          <t>H. &amp; T. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5853,7 +6861,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1481 RICHMOND WAY, Gwinnett County, GA</t>
+          <t>1481 RICHMOND [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5927,12 +6935,32 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>H. &amp; T. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>R7044 075</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>R7044 075</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -5952,10 +6980,14 @@
           <t>16 123 05 045</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>STELLA M TAYLOR ESTATE</t>
+          <t>S. &amp; M. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5971,7 +7003,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6472 BEDFORD LN, Lithonia, GA 30058</t>
+          <t>6472 BEDFORD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6001,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -6055,12 +7087,32 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>S. &amp; M. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>16 123 05 045</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>16 123 05 045</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6080,10 +7132,14 @@
           <t>R6321A014</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Parcel R632████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HOLCOMBE MARLON</t>
+          <t>H. &amp; M. M█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6099,7 +7155,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3557 KNOTSBERRY LN, Gwinnett County, GA</t>
+          <t>3557 KNOTSBERRY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6173,12 +7229,32 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>H. &amp; M. M█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>R6321A014</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>R6321A014</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6198,10 +7274,14 @@
           <t>15 220 09 014</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Parcel 15 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BRETT MULLINS</t>
+          <t>B. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6217,7 +7297,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2937 MONTEREY DR, Decatur, GA 30032</t>
+          <t>2937 MONTEREY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6247,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -6301,12 +7381,32 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>B. &amp; M. M██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>15 220 09 014</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>15 220 09 014</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6326,10 +7426,14 @@
           <t>16 009 02 036</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BOYD BROOKS &amp; LAKEMBA WARD</t>
+          <t>B. &amp; B. W████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6345,7 +7449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8 B QUAIL RUN, Decatur, GA 30035</t>
+          <t>8 B [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6375,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -6429,12 +7533,32 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>B. &amp; B. W████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>16 009 02 036</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>16 009 02 036</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6454,10 +7578,14 @@
           <t>R7259 221</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Parcel R725████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LAND BUFORD HWY</t>
+          <t>L. &amp; B. H████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6473,7 +7601,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20 LLC BUFORD DR, Gwinnett County, GA</t>
+          <t>20 LLC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6503,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -6557,12 +7685,32 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>L. &amp; B. H████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>R7259 221</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>R7259 221</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6582,10 +7730,14 @@
           <t>R7252 031</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Parcel R725████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PEACHTREE/SUWANEE</t>
+          <t>P. &amp; /. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6601,7 +7753,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PROP LTD PEACHTREE INDUSTRIAL BLVD, Gwinnett County, GA</t>
+          <t>PROP LTD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6631,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -6685,12 +7837,32 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>P. &amp; /. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>R7252 031</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>R7252 031</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6710,10 +7882,14 @@
           <t>15 229 05 019</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Parcel 15 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6729,7 +7905,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1 LLC 3812 KENSINGWOOD TRCE, Decatur, GA 30032</t>
+          <t>1 LLC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6759,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -6813,12 +7989,32 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>15 229 05 019</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>15 229 05 019</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6838,10 +8034,14 @@
           <t>R7093 009A</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Parcel R709████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SUNNY HILL HOME DEMON</t>
+          <t>S. &amp; H. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6857,7 +8057,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1799 BRASELTON HWY, Gwinnett County, GA</t>
+          <t>1799 BRASELTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6887,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -6941,12 +8141,32 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>S. &amp; H. D████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>R7093 009A</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>R7093 009A</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -6966,10 +8186,14 @@
           <t>18 013 06 001</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OSCAR O HERNANDEZ PADILLA</t>
+          <t>O. &amp; O. P██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6985,7 +8209,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>411 SAFARI CIRCLE, Stone Mountain, GA 30083</t>
+          <t>411 SAFARI [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7015,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -7069,12 +8293,32 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>O. &amp; O. P██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>18 013 06 001</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>18 013 06 001</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7094,10 +8338,14 @@
           <t>R6154 562</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Parcel R615████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OAKTREE</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7113,7 +8361,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MEADOWS HOMEOWNERS OAKTREE PARK CT, Gwinnett County, GA</t>
+          <t>MEADOWS HOMEOWNERS [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7143,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -7197,12 +8445,32 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>R6154 562</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>R6154 562</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7222,10 +8490,14 @@
           <t>16 153 08 047</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BRENDA PHILPOT</t>
+          <t>B. &amp; P. P██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7241,7 +8513,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7068 HAMMOND WAY, Lithonia, GA 30058</t>
+          <t>7068 HAMMOND [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7271,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -7325,12 +8597,32 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>B. &amp; P. P██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>16 153 08 047</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>16 153 08 047</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7350,10 +8642,14 @@
           <t>18 309 07 038</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Parcel 18 3████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NICK LONG JR ESTATE</t>
+          <t>N. &amp; L. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7369,7 +8665,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2302 TERRELL DR, Atlanta, GA 30341</t>
+          <t>2302 TERRELL [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7399,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -7453,12 +8749,32 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>N. &amp; L. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>18 309 07 038</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>18 309 07 038</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7478,10 +8794,14 @@
           <t>16 074 07 024</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BRETT O MULLINGS</t>
+          <t>B. &amp; O. M███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7497,7 +8817,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>131 TIBURON CT, Lithonia, GA 30038</t>
+          <t>131 TIBURON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7527,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -7581,12 +8901,32 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>B. &amp; O. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>16 074 07 024</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>16 074 07 024</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7606,10 +8946,14 @@
           <t>16 074 08 085</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NATHAN SMITH &amp; STEVEN HAMMOND &amp; DELITA D. PERRINO</t>
+          <t>N. &amp; S. P██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7625,7 +8969,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3068 PARC LORRAINE, Lithonia, GA 30038</t>
+          <t>3068 PARC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7655,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -7709,12 +9053,32 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>N. &amp; S. P██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>16 074 08 085</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>16 074 08 085</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7734,10 +9098,14 @@
           <t>15 090 06 039</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DREAM ILLUMINATION FOUNDATION</t>
+          <t>D. &amp; I. F█████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7753,7 +9121,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3229 STRAWBERRY LN, Decatur, GA 30034</t>
+          <t>3229 STRAWBERRY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7783,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -7837,12 +9205,32 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>D. &amp; I. F█████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>15 090 06 039</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>15 090 06 039</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7862,10 +9250,14 @@
           <t>16 152 11 020</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CALVIN CHAN</t>
+          <t>C. &amp; C. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7881,7 +9273,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7163 SWIFT ST, Lithonia, GA 30058</t>
+          <t>7163 SWIFT [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7911,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -7965,12 +9357,32 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>C. &amp; C. C████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>16 152 11 020</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>16 152 11 020</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -7990,10 +9402,14 @@
           <t>16 074 08 083</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NATHAN SMITH &amp; STEVEN HAMMOND &amp; LIANE TRUELL</t>
+          <t>N. &amp; S. T█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8009,7 +9425,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3070 PARC LORRAINE, Lithonia, GA 30038</t>
+          <t>3070 PARC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8039,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -8093,12 +9509,32 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>N. &amp; S. T█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>16 074 08 083</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>16 074 08 083</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8118,10 +9554,14 @@
           <t>16 141 02 013</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DONOVAN SQUIRES</t>
+          <t>D. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -8137,7 +9577,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6794 ROCKLAND ROAD, Lithonia, GA 30038</t>
+          <t>6794 ROCKLAND [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8167,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -8221,12 +9661,32 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>D. &amp; S. S██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>16 141 02 013</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>16 141 02 013</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8246,10 +9706,14 @@
           <t>16 074 08 095</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NATHAN SMITH &amp; MARY ELIZABETH HIRSCH</t>
+          <t>N. &amp; S. H█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8265,7 +9729,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3076 PARC LORRAINE, Lithonia, GA 30038</t>
+          <t>3076 PARC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8295,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -8349,12 +9813,32 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>N. &amp; S. H█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>16 074 08 095</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>16 074 08 095</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8374,10 +9858,14 @@
           <t>15 193 04 026</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AKIM RAVARIERE &amp; MELINA RAVARIERE</t>
+          <t>A. &amp; R. R████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8393,7 +9881,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1541 WALNUT RIDGE COURT, Stone Mountain, GA 30083</t>
+          <t>1541 WALNUT [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8423,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -8477,12 +9965,32 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>A. &amp; R. R████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>15 193 04 026</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>15 193 04 026</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8502,10 +10010,14 @@
           <t>15 181 05 018</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ZION TASHKENT TASHKENT</t>
+          <t>Z. &amp; T. T███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8521,7 +10033,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2451 MEMORIAL DR, Atlanta, GA 30317</t>
+          <t>2451 MEMORIAL [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8551,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -8605,12 +10117,32 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Z. &amp; T. T███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>15 181 05 018</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>15 181 05 018</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8630,10 +10162,14 @@
           <t>15 101 01 005</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>STEVEN EDWARD BRIEN</t>
+          <t>S. &amp; E. B████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8649,7 +10185,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3632 FREDA CT, Decatur, GA 30034</t>
+          <t>3632 FREDA [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8679,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -8733,12 +10269,32 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>S. &amp; E. B████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>15 101 01 005</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>15 101 01 005</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8758,10 +10314,14 @@
           <t>18 224 01 020</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>NOAH DOSS</t>
+          <t>N. &amp; D. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -8777,7 +10337,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4488 LAWRENCEVILLE HWY, Tucker, GA 30084</t>
+          <t>4488 LAWRENCEVILLE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8807,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -8861,12 +10421,32 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>N. &amp; D. D████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>18 224 01 020</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>18 224 01 020</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -8886,10 +10466,14 @@
           <t>18 046 03 070</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MOSELY FREDRICK HIS ESTATE PERS REP AND HEIRS KNOWN AND UNKNOWN</t>
+          <t>M. &amp; F. U██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -8905,7 +10489,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3194 ALTACREST DR, Scottdale, GA 30079</t>
+          <t>3194 ALTACREST [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8935,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -8989,12 +10573,32 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>M. &amp; F. U██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>18 046 03 070</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>18 046 03 070</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9014,10 +10618,14 @@
           <t>16 153 08 006</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RHONEIA N STARKS</t>
+          <t>R. &amp; N. S█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9033,7 +10641,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7079 PINE MOUNTAIN RD, Lithonia, GA 30058</t>
+          <t>7079 PINE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9063,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -9117,12 +10725,32 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>R. &amp; N. S█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>16 153 08 006</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>16 153 08 006</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9142,10 +10770,14 @@
           <t>15 093 07 006</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>U S HOUSING &amp; URBAN DEV</t>
+          <t>U. &amp; S. D████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9161,7 +10793,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3181 WESLEY CHAPEL ROAD, Decatur, GA 30034</t>
+          <t>3181 WESLEY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9191,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -9245,12 +10877,32 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>U. &amp; S. D████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>15 093 07 006</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>15 093 07 006</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9270,10 +10922,14 @@
           <t>18 341 10 001</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Parcel 18 3████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DAVID CHESTNUT</t>
+          <t>D. &amp; C. C███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9289,7 +10945,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2625 HOMELAND DR, Atlanta, GA 30360</t>
+          <t>2625 HOMELAND [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9319,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -9373,12 +11029,32 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>D. &amp; C. C███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>18 341 10 001</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>18 341 10 001</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9398,10 +11074,14 @@
           <t>16 074 08 092</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PATRICIA ANN MARSHALL</t>
+          <t>P. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9417,7 +11097,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3078 PARC LORRAINE, Lithonia, GA 30038</t>
+          <t>3078 PARC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9447,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -9501,12 +11181,32 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>P. &amp; A. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>16 074 08 092</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>16 074 08 092</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9526,10 +11226,14 @@
           <t>R5005 149</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Parcel R500████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>WEIDLICH</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9545,7 +11249,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PAUL GREENVALLEY RD, Gwinnett County, GA</t>
+          <t>PAUL GREENVALLEY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9575,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -9629,12 +11333,32 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>R5005 149</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>R5005 149</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9654,10 +11378,14 @@
           <t>16 074 07 016</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TOSHA DEACON</t>
+          <t>T. &amp; D. D█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9673,7 +11401,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>113 TIBURON CT, Lithonia, GA 30038</t>
+          <t>113 TIBURON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9703,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -9757,12 +11485,32 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>T. &amp; D. D█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>16 074 07 016</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>16 074 07 016</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9782,10 +11530,14 @@
           <t>R7266 232</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Parcel R726████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ARONSON</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9801,7 +11553,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MARCEEN LEE ARDEN DR, Gwinnett County, GA</t>
+          <t>MARCEEN LEE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9831,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -9885,12 +11637,32 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>R7266 232</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>R7266 232</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -9910,10 +11682,14 @@
           <t>R4346A168</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Parcel R434████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DENSON</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9929,7 +11705,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>CONNIE MARJORIE RD, Gwinnett County, GA</t>
+          <t>CONNIE MARJORIE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9959,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -10013,12 +11789,32 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>R4346A168</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>R4346A168</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10038,10 +11834,14 @@
           <t>18 046 03 087</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SCOTT JOHN GILBERT</t>
+          <t>S. &amp; J. G██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -10057,7 +11857,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3171 ALTACREST DR, Scottdale, GA 30079</t>
+          <t>3171 ALTACREST [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10087,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -10141,12 +11941,32 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>S. &amp; J. G██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>18 046 03 087</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>18 046 03 087</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10166,10 +11986,14 @@
           <t>15 090 07 013</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RODRIGUEZ MARTA GRANDA LIVING RODRIGUEZ MARTA G</t>
+          <t>R. &amp; M. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -10185,7 +12009,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3155 CITRUS CT, Decatur, GA 30034</t>
+          <t>3155 CITRUS [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10215,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -10269,12 +12093,32 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>R. &amp; M. G████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>15 090 07 013</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>15 090 07 013</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10294,10 +12138,14 @@
           <t>R7305 083</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Parcel R730████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GARMON EVERETT E ETAL</t>
+          <t>G. &amp; E. E████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -10313,7 +12161,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1332 CRAIG DR, Gwinnett County, GA</t>
+          <t>1332 CRAIG [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10343,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -10397,12 +12245,32 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>G. &amp; E. E████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>R7305 083</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>R7305 083</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10422,10 +12290,14 @@
           <t>R6058 137</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Parcel R605████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JERE M.</t>
+          <t>J. &amp; M. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10441,7 +12313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>POWER ROCKBRIDGE RD, Gwinnett County, GA</t>
+          <t>POWER ROCKBRIDGE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10471,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -10525,12 +12397,32 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>J. &amp; M. M████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>R6058 137</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>R6058 137</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10550,10 +12442,14 @@
           <t>R6281 018</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Parcel R628████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BAY COLONY PROPERTY CO JONES MILL RD</t>
+          <t>B. &amp; C. R████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -10569,7 +12465,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Gwinnett County, GA</t>
+          <t>Gwinnett County, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10599,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -10653,12 +12549,32 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>B. &amp; C. R████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>R6281 018</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>R6281 018</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10678,10 +12594,14 @@
           <t>18 126 15 012</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Parcel 18 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ROSA REID ESTATE</t>
+          <t>R. &amp; R. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -10697,7 +12617,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>6726 STEVILLE ST, Stone Mountain, GA 30083</t>
+          <t>6726 STEVILLE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10727,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -10781,12 +12701,32 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>R. &amp; R. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>18 126 15 012</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>18 126 15 012</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10806,10 +12746,14 @@
           <t>18 015 06 013</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>A AND A INVESTMENT AND</t>
+          <t>A. &amp; A. A████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -10825,7 +12769,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>514 ALLGOOD ROAD, Stone Mountain, GA 30083</t>
+          <t>514 ALLGOOD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10855,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -10909,12 +12853,32 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>A. &amp; A. A████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>18 015 06 013</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>18 015 06 013</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -10934,10 +12898,14 @@
           <t>R6109 102</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Parcel R610████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -10953,7 +12921,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ALLEN R ETAL TAMER LN, Gwinnett County, GA</t>
+          <t>ALLEN R [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11027,12 +12995,32 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>R6109 102</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>R6109 102</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11052,10 +13040,14 @@
           <t>R6095 088</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Parcel R609████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CRUSSELLE</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -11071,7 +13063,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ARTHUR B ETAL MOUNTAIN WOODS CT, Gwinnett County, GA</t>
+          <t>ARTHUR B [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11101,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -11155,12 +13147,32 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>R6095 088</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>R6095 088</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11180,10 +13192,14 @@
           <t>15 192 02 010</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ELVIA PELAYO</t>
+          <t>E. &amp; P. P█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -11199,7 +13215,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1828 S HAIRSTON RD, Stone Mountain, GA 30088</t>
+          <t>1828 S [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11229,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -11283,12 +13299,32 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>E. &amp; P. P█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>15 192 02 010</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>15 192 02 010</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11308,10 +13344,14 @@
           <t>R4346A247</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Parcel R434████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BENJAMIN</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -11327,7 +13367,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ELLIS SCOTT BRADLEY DR, Gwinnett County, GA</t>
+          <t>ELLIS SCOTT [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11401,12 +13441,32 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>R4346A247</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>R4346A247</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11426,10 +13486,14 @@
           <t>16 046 01 098</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ANNMARIE PLUMMER-BAILEY</t>
+          <t>A. &amp; P. P█████████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -11445,7 +13509,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3954 E SADDLERIDGE DRIVE, Lithonia, GA 30038</t>
+          <t>3954 E [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11475,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-143</v>
+        <v>-145</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -11529,12 +13593,32 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>A. &amp; P. P█████████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>16 046 01 098</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>16 046 01 098</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11554,10 +13638,14 @@
           <t>18 068 11 027</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ABDULKADIR AHMED</t>
+          <t>A. &amp; A. A████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -11573,7 +13661,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6722 BAYNES HILL CIR, Clarkston, GA 30021</t>
+          <t>6722 BAYNES [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11603,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -11657,12 +13745,32 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>A. &amp; A. A████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>18 068 11 027</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>18 068 11 027</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11682,10 +13790,14 @@
           <t>R4348A062</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Parcel R434████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MARY</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -11701,7 +13813,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>FITZGERALD WALLACE CIR, Gwinnett County, GA</t>
+          <t>FITZGERALD WALLACE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11731,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -11785,12 +13897,32 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>R4348A062</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>R4348A062</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11810,10 +13942,14 @@
           <t>16 218 03 082</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Parcel 16 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MICHAEL BOWMAN</t>
+          <t>M. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -11829,7 +13965,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2443 HARMONY RIDGE CT, Lithonia, GA 30058</t>
+          <t>2443 HARMONY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11859,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -11913,12 +14049,32 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>M. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>16 218 03 082</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>16 218 03 082</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -11938,10 +14094,14 @@
           <t>18 047 23 022</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MARY ANN EDWARDS ESTATE</t>
+          <t>M. &amp; A. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -11957,7 +14117,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>457 PROCTOR AVE, Scottdale, GA 30079</t>
+          <t>457 PROCTOR [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11987,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -12041,12 +14201,32 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>M. &amp; A. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>18 047 23 022</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>18 047 23 022</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12066,10 +14246,14 @@
           <t>R6067 098</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Parcel R606████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BUTSCH</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -12085,7 +14269,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>GLENDEAN B OAK DR, Gwinnett County, GA</t>
+          <t>GLENDEAN B [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -12115,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -12169,12 +14353,32 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>R6067 098</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>R6067 098</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12194,10 +14398,14 @@
           <t>18 044 09 059</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JIMMY L JACKSON &amp; MABLE MCWHORTER JACKSON</t>
+          <t>J. &amp; L. J██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -12213,7 +14421,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>528 RIDGECREEK DR, Clarkston, GA 30021</t>
+          <t>528 RIDGECREEK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -12243,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -12297,12 +14505,32 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>J. &amp; L. J██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>18 044 09 059</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>18 044 09 059</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12322,10 +14550,14 @@
           <t>15 096 02 121</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CECIL DAVIS ESTATE</t>
+          <t>C. &amp; D. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -12341,7 +14573,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3137 NORTHCHESTER PLACE, Lithonia, GA 30038</t>
+          <t>3137 NORTHCHESTER [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -12371,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -12425,12 +14657,32 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>C. &amp; D. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>15 096 02 121</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>15 096 02 121</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12450,10 +14702,14 @@
           <t>15 027 01 090</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RIVER MILL ROCK MILL CLUB MILL</t>
+          <t>R. &amp; M. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -12469,7 +14725,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3489 RIVER MILL LN, Ellenwood, GA 30294</t>
+          <t>3489 RIVER [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12499,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -12553,12 +14809,32 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>R. &amp; M. M████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>15 027 01 090</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>15 027 01 090</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12578,10 +14854,14 @@
           <t>18 044 09 080</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CHARLES E ANDERSON ESTATE</t>
+          <t>C. &amp; E. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -12597,7 +14877,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>418 RIDGECREEK DR, Clarkston, GA 30021</t>
+          <t>418 RIDGECREEK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12627,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -12681,12 +14961,32 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>C. &amp; E. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>18 044 09 080</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>18 044 09 080</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12706,10 +15006,14 @@
           <t>18 073 01 161</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SABRINA YOUNG</t>
+          <t>S. &amp; Y. Y████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -12725,7 +15029,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>5274 SHEPPARD LANE, Stone Mountain, GA 30083</t>
+          <t>5274 SHEPPARD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12755,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -12809,12 +15113,32 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>S. &amp; Y. Y████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>18 073 01 161</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>18 073 01 161</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12834,10 +15158,14 @@
           <t>18 004 17 061</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HOWARD TOMMY EUGENE HOWARD MARY LEE</t>
+          <t>H. &amp; T. L████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -12853,7 +15181,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>289 DURAND FALLS DR, Decatur, GA 30030</t>
+          <t>289 DURAND [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12883,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -12937,12 +15265,32 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>H. &amp; T. L████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>18 004 17 061</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>18 004 17 061</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -12962,10 +15310,14 @@
           <t>R6276 022</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Parcel R627████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BAY COLONY PROPERTY CO JONES MILL CT</t>
+          <t>B. &amp; C. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -12981,7 +15333,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Gwinnett County, GA</t>
+          <t>Gwinnett County, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -13011,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -13065,12 +15417,32 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>B. &amp; C. C████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>R6276 022</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>R6276 022</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13090,10 +15462,14 @@
           <t>15 156 03 001</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>YARED BEEWKETU KASEG</t>
+          <t>Y. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -13109,7 +15485,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2229 TITAN RIDGE DRIVE, Decatur, GA 30035</t>
+          <t>2229 TITAN [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -13139,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -13193,12 +15569,32 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Y. &amp; B. K████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>15 156 03 001</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>15 156 03 001</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13218,10 +15614,14 @@
           <t>18 225 02 003</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CHANEREE THIEN</t>
+          <t>C. &amp; T. T████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13237,7 +15637,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2480 OLD NORCROSS RD, Tucker, GA 30084</t>
+          <t>2480 OLD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -13267,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -13321,12 +15721,32 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>C. &amp; T. T████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>18 225 02 003</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>18 225 02 003</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13346,10 +15766,14 @@
           <t>R6128 123</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Parcel R612████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BRENTWOOD-GLOSTER</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -13365,7 +15789,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>HOMEOWNERS ASSOCIATION INC HEATHGATE DR, Gwinnett County, GA</t>
+          <t>HOMEOWNERS ASSOCIATION [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -13395,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -13449,12 +15873,32 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>R6128 123</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>R6128 123</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13474,10 +15918,14 @@
           <t>16 074 14 029</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>JERMAINE PREDESTIN &amp; REGINA MENDEZ</t>
+          <t>J. &amp; P. M█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -13493,7 +15941,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2304 FAIRINGTON VILLAGE DR, Lithonia, GA 30038</t>
+          <t>2304 FAIRINGTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13523,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -13577,12 +16025,32 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>J. &amp; P. M█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>16 074 14 029</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>16 074 14 029</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13602,10 +16070,14 @@
           <t>R5140 189</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Parcel R514████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SIBLEY</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -13621,7 +16093,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>JAMES BLACK OAK CT, Gwinnett County, GA</t>
+          <t>JAMES BLACK [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13695,12 +16167,32 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>R5140 189</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>R5140 189</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13720,10 +16212,14 @@
           <t>18 187 01 246</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Parcel 18 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>C.O. EDWARDS &amp; CARL M. CAIN</t>
+          <t>C. &amp; E. C████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -13739,7 +16235,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2065 SHADY LANE, Tucker, GA 30084</t>
+          <t>2065 SHADY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13769,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -13823,12 +16319,32 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>C. &amp; E. C████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>18 187 01 246</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>18 187 01 246</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13848,10 +16364,14 @@
           <t>16 137 08 011</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>NANCY L KENNEDY</t>
+          <t>N. &amp; L. K██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -13867,7 +16387,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2703 WMS GRANT REYNOLDS DRIVE, Lithonia, GA 30058</t>
+          <t>2703 WMS [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -13897,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -13951,12 +16471,32 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>N. &amp; L. K██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>16 137 08 011</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>16 137 08 011</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -13976,10 +16516,14 @@
           <t>18 046 03 106</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CRONAN BROTHERS</t>
+          <t>C. &amp; B. B███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -13995,7 +16539,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3159 ALTACREST DR, Scottdale, GA 30079</t>
+          <t>3159 ALTACREST [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -14025,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -14079,12 +16623,32 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>C. &amp; B. B███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>18 046 03 106</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>18 046 03 106</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14104,10 +16668,14 @@
           <t>R4348A061</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Parcel R434████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MARY</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -14123,7 +16691,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FITZGERALD WALLACE CIR, Gwinnett County, GA</t>
+          <t>FITZGERALD WALLACE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -14153,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -14207,12 +16775,32 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>R4348A061</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>R4348A061</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14232,10 +16820,14 @@
           <t>16 043 03 078</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>WILLIAM H ROBINSON JR ESTATE</t>
+          <t>W. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -14251,7 +16843,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>3366 PANOLA RD, Lithonia, GA 30038</t>
+          <t>3366 PANOLA [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14281,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -14335,12 +16927,32 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>W. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>16 043 03 078</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>16 043 03 078</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14360,10 +16972,14 @@
           <t>18 046 03 060</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>GWENDOLYN HEATH ESTATE</t>
+          <t>G. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -14379,7 +16995,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>457 3RD AVENUE NE, Scottdale, GA 30079</t>
+          <t>457 3RD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -14409,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -14463,12 +17079,32 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>G. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>18 046 03 060</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>18 046 03 060</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14488,10 +17124,14 @@
           <t>18 018 01 121</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>MONICA BOBB BOWMAN</t>
+          <t>M. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -14507,7 +17147,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5175 SELENE DR, Stone Mountain, GA 30088</t>
+          <t>5175 SELENE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14537,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -14591,12 +17231,32 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>M. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>18 018 01 121</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>18 018 01 121</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14616,10 +17276,14 @@
           <t>18 046 03 093</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UNKNOWN OWNER - UNRETURNED PROPERTY</t>
+          <t>U. &amp; O. P███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -14635,7 +17299,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3170 KELLY ST, Scottdale, GA 30079</t>
+          <t>3170 KELLY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -14665,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -14719,12 +17383,32 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>U. &amp; O. P███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>18 046 03 093</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>18 046 03 093</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14744,10 +17428,14 @@
           <t>18 046 03 051</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ALICE WATKINS</t>
+          <t>A. &amp; W. W██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -14763,7 +17451,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3160 BLANTON DR, Scottdale, GA 30079</t>
+          <t>3160 BLANTON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -14793,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -14847,12 +17535,32 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>A. &amp; W. W██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>18 046 03 051</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>18 046 03 051</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -14872,10 +17580,14 @@
           <t>18 046 03 211</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>BOYD MARIE HER ESTATE ADMINISTRATOR EXECUTOR AND HEIRS KNOWN AND UNKNOWN</t>
+          <t>B. &amp; M. U██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -14891,7 +17603,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3222 ALTACREST DR, Scottdale, GA 30079</t>
+          <t>3222 ALTACREST [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -14921,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -14975,12 +17687,32 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>B. &amp; M. U██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>18 046 03 211</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>18 046 03 211</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15000,10 +17732,14 @@
           <t>18 046 03 069</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MARY M MATTHEWS</t>
+          <t>M. &amp; M. M███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -15019,7 +17755,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3192 ALTACREST DR, Scottdale, GA 30079</t>
+          <t>3192 ALTACREST [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -15049,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -15103,12 +17839,32 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>M. &amp; M. M███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>18 046 03 069</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>18 046 03 069</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15128,10 +17884,14 @@
           <t>16 140 02 012</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>WILLIAM H. BROOKS ESTATE</t>
+          <t>W. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -15147,7 +17907,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3403 PLUNKETT ROAD, Lithonia, GA 30038</t>
+          <t>3403 PLUNKETT [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -15177,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -15231,12 +17991,32 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>W. &amp; H. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>16 140 02 012</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>16 140 02 012</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15256,10 +18036,14 @@
           <t>18 046 03 037</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>JAMES GRESHAM</t>
+          <t>J. &amp; G. G██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -15275,7 +18059,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3195 ROBINSON AVE, Scottdale, GA 30079</t>
+          <t>3195 ROBINSON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -15305,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -15359,12 +18143,32 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>J. &amp; G. G██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>18 046 03 037</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>18 046 03 037</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15384,10 +18188,14 @@
           <t>18 046 03 236</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>GALLOWAY JAMES ESTATE PERS REP AND HEIRS KNOWN AND UNKNOWN</t>
+          <t>G. &amp; J. U██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -15403,7 +18211,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>3248 KELLY ST, Scottdale, GA 30079</t>
+          <t>3248 KELLY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -15433,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -15487,12 +18295,32 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>G. &amp; J. U██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>18 046 03 236</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>18 046 03 236</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15512,26 +18340,30 @@
           <t>18 047 26 017</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MARY EMILY &amp; SURVARIA BREWER ESTATES</t>
+          <t>M. &amp; E. E██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
+          <t>Individual / Estate</t>
         </is>
       </c>
       <c r="G119" t="b">
         <v>1</v>
       </c>
       <c r="H119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>3132 WALKER ST, Scottdale, GA 30079</t>
+          <t>3132 WALKER [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15561,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -15615,12 +18447,32 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>M. &amp; E. E██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>18 047 26 017</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>18 047 26 017</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15640,10 +18492,14 @@
           <t>R6154 569</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Parcel R615████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OAKTREE</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -15659,7 +18515,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>MEADOWS HOMEOWNERS OAKTREE PARK CT, Gwinnett County, GA</t>
+          <t>MEADOWS HOMEOWNERS [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -15689,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -15743,12 +18599,32 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>R6154 569</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>R6154 569</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15768,10 +18644,14 @@
           <t>R6183 166</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Parcel R618████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HICKORY</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -15787,7 +18667,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PLANTATION HOMEOWNERS ANVIL CT, Gwinnett County, GA</t>
+          <t>PLANTATION HOMEOWNERS [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -15817,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -15871,12 +18751,32 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>R6183 166</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>R6183 166</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -15896,10 +18796,14 @@
           <t>15 199 04 193</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>GETHSEMANE TEMPLE AFFILIATED WITH UHC</t>
+          <t>G. &amp; T. U████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -15915,7 +18819,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3237 MIDWAY RD, Decatur, GA 30032</t>
+          <t>3237 MIDWAY [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -15945,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -15999,12 +18903,32 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>G. &amp; T. U████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>15 199 04 193</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>15 199 04 193</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16024,10 +18948,14 @@
           <t>18 203 06 069</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MCJENKIN ESTHER H MRS</t>
+          <t>M. &amp; E. M████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -16043,7 +18971,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1828 R MCJENKIN DR, Atlanta, GA 30345</t>
+          <t>1828 R [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -16073,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -16127,12 +19055,32 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>M. &amp; E. M████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>18 203 06 069</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>18 203 06 069</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16152,10 +19100,14 @@
           <t>18 046 03 067</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UNKNOWN OWNER - UNRETURNED PROPERTY 3180 altacrest dr SCOTTDALE 30079</t>
+          <t>U. &amp; O. 3████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -16171,7 +19123,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DeKalb County, GA</t>
+          <t>DeKalb County, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -16201,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -16255,12 +19207,32 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>U. &amp; O. 3████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>18 046 03 067</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>18 046 03 067</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16280,10 +19252,14 @@
           <t>18 081 05 073</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ANNMARIE PLUMMER BAILEY &amp; WINSTON BAILEY</t>
+          <t>A. &amp; P. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -16299,7 +19275,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6914 DOCKBRIDGE WAY, Stone Mountain, GA 30087</t>
+          <t>6914 DOCKBRIDGE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -16329,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -16383,12 +19359,32 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>A. &amp; P. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>18 081 05 073</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>18 081 05 073</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16408,10 +19404,14 @@
           <t>R7069 420</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Parcel R706████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>STERLING</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -16427,7 +19427,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>MANOR DEV INC PENNY LN, Gwinnett County, GA</t>
+          <t>MANOR DEV [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -16457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -16511,12 +19511,32 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>R7069 420</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>R7069 420</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16536,10 +19556,14 @@
           <t>15 122 06 066</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>EDGAR DUNCAN</t>
+          <t>E. &amp; D. D█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -16555,7 +19579,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3232 ABBEYWOOD DRIVE, Decatur, GA 30034</t>
+          <t>3232 ABBEYWOOD [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -16585,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-45</v>
+        <v>-47</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -16639,12 +19663,32 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>E. &amp; D. D█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>15 122 06 066</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>15 122 06 066</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16664,10 +19708,14 @@
           <t>18 046 03 011</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FRED WILLIAMS ESTATE</t>
+          <t>F. &amp; W. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -16683,7 +19731,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3194 ROBINSON AVE, Scottdale, GA 30079</t>
+          <t>3194 ROBINSON [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16713,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -16767,12 +19815,32 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>F. &amp; W. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>18 046 03 011</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>18 046 03 011</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16792,10 +19860,14 @@
           <t>R6120 107</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Parcel R612████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>W W BUILDERS</t>
+          <t>W. &amp; W. B███████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -16811,7 +19883,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>5538 FERN CREEK DR, Gwinnett County, GA</t>
+          <t>5538 FERN [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -16841,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -16895,12 +19967,32 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>W. &amp; W. B███████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>R6120 107</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>R6120 107</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -16920,10 +20012,14 @@
           <t>18 047 23 016</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Parcel 18 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>BROWN JOHNSON</t>
+          <t>B. &amp; J. J██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -16939,7 +20035,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>458 BOOKER AVE, Scottdale, GA 30079</t>
+          <t>458 BOOKER [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -16969,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -17023,12 +20119,32 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>B. &amp; J. J██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>18 047 23 016</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>18 047 23 016</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17048,10 +20164,14 @@
           <t>15 058 05 035</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Parcel 15 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LEROY HARDING 3289 BLAZING PINE KNL #A DECATUR 30034</t>
+          <t>L. &amp; H. 3████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -17067,7 +20187,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>DeKalb County, GA</t>
+          <t>DeKalb County, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -17097,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -17151,12 +20271,32 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>L. &amp; H. 3████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>15 058 05 035</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>15 058 05 035</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17176,10 +20316,14 @@
           <t>18 225 03 022</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Parcel 18 2████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P D HOPKINS</t>
+          <t>P. &amp; D. H██████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -17195,7 +20339,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2520 PINE LAKE PL, Tucker, GA 30084</t>
+          <t>2520 PINE [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -17225,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -17279,12 +20423,32 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>P. &amp; D. H██████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>18 225 03 022</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>18 225 03 022</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17304,10 +20468,14 @@
           <t>R6114 027</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Parcel R611████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CELESTINO MACEDO-JAMES</t>
+          <t>C. &amp; M. M███████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -17323,7 +20491,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>WYDELLA RD, Gwinnett County, GA</t>
+          <t>WYDELLA RD, [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -17353,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -17407,12 +20575,32 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>C. &amp; M. M███████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>R6114 027</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>R6114 027</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17432,10 +20620,14 @@
           <t>R5137 171</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Parcel R513████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>BP DIVERSIFIED ASSETS GROUP</t>
+          <t>B. &amp; D. G████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -17451,7 +20643,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>368 BRACKIN TRACE, Gwinnett County, GA</t>
+          <t>368 BRACKIN [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -17481,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -17535,12 +20727,32 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>B. &amp; D. G████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>R5137 171</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>R5137 171</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17560,10 +20772,14 @@
           <t>16 074 08 101</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ETHEL J MABRY ESTATE</t>
+          <t>E. &amp; J. E█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -17579,7 +20795,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3102 PARC LORRAINE, Lithonia, GA 30038</t>
+          <t>3102 PARC [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17609,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -17663,12 +20879,32 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>E. &amp; J. E█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>16 074 08 101</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>16 074 08 101</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17688,10 +20924,14 @@
           <t>R4349 085</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Parcel R434████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ELITE</t>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -17707,7 +20947,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>REALTY GROUP INC HIGHTOWER TRAIL, Gwinnett County, GA</t>
+          <t>REALTY GROUP [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -17737,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -17791,12 +21031,32 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:41Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>[REDACTED — SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>R4349 085</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>R4349 085</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17816,10 +21076,14 @@
           <t>15 174 08 067</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>W C ELLINGTON</t>
+          <t>W. &amp; C. E████████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -17835,7 +21099,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>694 R CLIFTON RD S, Atlanta, GA 30316</t>
+          <t>694 R [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -17865,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -17919,12 +21183,32 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>W. &amp; C. E████████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>15 174 08 067</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>15 174 08 067</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -17944,10 +21228,14 @@
           <t>16 009 02 005</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Parcel 16 0████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ROSE BURNEY</t>
+          <t>R. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -17963,7 +21251,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>28 QUAIL RUN, Decatur, GA 30035</t>
+          <t>28 QUAIL [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17993,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -18047,12 +21335,32 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>R. &amp; B. B█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>16 009 02 005</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>16 009 02 005</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -18072,10 +21380,14 @@
           <t>15 191 01 108</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Parcel 15 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>BRUCE T HANSEN</t>
+          <t>B. &amp; T. H█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -18091,7 +21403,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4380 CEDAR RIDGE TRL, Stone Mountain, GA 30083</t>
+          <t>4380 CEDAR [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -18121,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -18175,12 +21487,32 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>B. &amp; T. H█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>15 191 01 108</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>15 191 01 108</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>
@@ -18200,10 +21532,14 @@
           <t>16 169 07 061</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Parcel 16 1████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>TOMMIE ABBOTT</t>
+          <t>T. &amp; A. A█████ [SUBSCRIBER KEY REQUIRED]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18219,7 +21555,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>7089 MCDANIEL ST, Lithonia, GA 30058</t>
+          <t>7089 MCDANIEL [REDACTED — SUBSCRIBER ACCESS ONLY]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -18249,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -18303,12 +21639,32 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:38Z</t>
+          <t>2026-10-22T09:22:40Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-22 09:22:48</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>T. &amp; A. A█████ [SUBSCRIBER KEY REQUIRED]</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>16 169 07 061</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>16 169 07 061</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>REDACTED_PREVIEW</t>
         </is>
       </c>
     </row>

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-145</v>
+        <v>-146</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:41Z</t>
+          <t>2026-10-23T09:18:55Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:40Z</t>
+          <t>2026-10-23T09:18:54Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:55Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:54Z</t>
+          <t>2026-10-24T08:50:35Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-147</v>
+        <v>-148</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:19Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:35Z</t>
+          <t>2026-10-25T09:07:18Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-148</v>
+        <v>-149</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-87</v>
+        <v>-88</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:19Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:18Z</t>
+          <t>2026-10-26T10:03:11Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-88</v>
+        <v>-89</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:11Z</t>
+          <t>2026-10-27T09:47:09Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:07Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:09Z</t>
+          <t>2026-10-28T10:32:06Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:07Z</t>
+          <t>2026-10-29T10:51:36Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:06Z</t>
+          <t>2026-10-29T10:51:35Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,11 +11279,11 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-152</v>
+        <v>-153</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:36Z</t>
+          <t>2026-10-30T10:50:39Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:35Z</t>
+          <t>2026-10-30T10:50:38Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">

--- a/site/exports/Georgia_Surplus_Feed.xlsx
+++ b/site/exports/Georgia_Surplus_Feed.xlsx
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4817,12 +4817,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6283,7 +6283,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -9509,12 +9509,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -10421,12 +10421,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11485,12 +11485,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11941,12 +11941,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -12093,12 +12093,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -12549,12 +12549,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12853,12 +12853,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12995,12 +12995,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -13147,12 +13147,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -13745,12 +13745,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -13897,12 +13897,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -14201,12 +14201,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -14299,7 +14299,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -14505,12 +14505,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -14755,7 +14755,7 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -14809,12 +14809,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -14961,12 +14961,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -15265,12 +15265,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -15417,12 +15417,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -15569,12 +15569,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -15667,7 +15667,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -15873,12 +15873,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -15971,7 +15971,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -16025,12 +16025,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -16167,12 +16167,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -16319,12 +16319,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -16569,7 +16569,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -16623,12 +16623,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -16721,7 +16721,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -16775,12 +16775,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -17079,12 +17079,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -17177,7 +17177,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -17231,12 +17231,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -17383,12 +17383,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -17481,7 +17481,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -17535,12 +17535,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -17633,7 +17633,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -17839,12 +17839,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -17937,7 +17937,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -17991,12 +17991,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -18393,7 +18393,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -18599,12 +18599,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -18697,7 +18697,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-92</v>
+        <v>-93</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -18751,12 +18751,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -19055,12 +19055,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -19207,12 +19207,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -19305,7 +19305,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -19761,7 +19761,7 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -19815,12 +19815,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -19913,7 +19913,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -19967,12 +19967,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -20119,12 +20119,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -20271,12 +20271,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -20423,12 +20423,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -20575,12 +20575,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -20727,12 +20727,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -20879,12 +20879,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:39Z</t>
+          <t>2026-10-31T10:21:07Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -21183,12 +21183,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -21281,7 +21281,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -21433,7 +21433,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -21585,7 +21585,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -21639,12 +21639,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:38Z</t>
+          <t>2026-10-31T10:21:06Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
